--- a/AAII_Financials/Quarterly/BXSL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BXSL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>BXSL</t>
   </si>
@@ -656,238 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>304300</v>
+      </c>
+      <c r="E8" s="3">
         <v>284000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>290400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>264900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>250900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>226800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>187000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>185600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>192000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>166900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>135100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>130700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>136700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>91600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>81200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>80200</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>125900</v>
+      </c>
+      <c r="E9" s="3">
         <v>112300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>114200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>111500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>106400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>97000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>82600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>78000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>77200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>65300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>54400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>47300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>46300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>33300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>30600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>178400</v>
+      </c>
+      <c r="E10" s="3">
         <v>171700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>176200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>153400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>144500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>129800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>104400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>107600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>114800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>101600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>80700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>83400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>90400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>58300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>50600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>49200</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -906,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -956,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,8 +1022,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1056,8 +1075,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1106,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>127600</v>
+      </c>
+      <c r="E17" s="3">
         <v>118200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>113900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>113100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>107300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>94600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>81700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>81500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>81000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>70800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>63700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>55100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>51100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>36300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>32700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>176700</v>
+      </c>
+      <c r="E18" s="3">
         <v>165800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>176500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>151800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>143700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>132200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>105300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>104100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>111000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>96100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>71400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>75600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>85600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>55300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>48500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>50800</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,58 +1275,62 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="E20" s="3">
         <v>10200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-26700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-10300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-21900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-36200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-25700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>16200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>45300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>35900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>35600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>121000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>180500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-358100</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1343,8 +1379,11 @@
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1393,73 +1432,79 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>161500</v>
+      </c>
+      <c r="E23" s="3">
         <v>176000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>149800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>141400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>121800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>95900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>79600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>108600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>122500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>112200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>116700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>111500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>121200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>176300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>229000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-307400</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>5000</v>
+        <v>4200</v>
       </c>
       <c r="E24" s="3">
         <v>5000</v>
       </c>
       <c r="F24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G24" s="3">
         <v>2600</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
@@ -1467,34 +1512,37 @@
         <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>1400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2200</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3" t="s">
+      <c r="Q24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>157300</v>
+      </c>
+      <c r="E26" s="3">
         <v>171000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>144900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>138800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>121800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>95900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>79600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>107200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>122000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>110000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>116700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>111800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>120800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>176300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>229000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>157300</v>
+      </c>
+      <c r="E27" s="3">
         <v>171000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>144900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>138800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>121800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>95900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>79600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>107200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>122000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>110000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>116700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>111800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>120800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>176300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>229000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>26700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>10300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>21900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>36200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>25700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-16200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-45300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-35900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-35600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-121000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-180500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>358100</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>157300</v>
+      </c>
+      <c r="E33" s="3">
         <v>171000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>144900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>138800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>121800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>95900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>79600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>107200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>122000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>110000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>116700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>111800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>120800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>176300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>229000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>157300</v>
+      </c>
+      <c r="E35" s="3">
         <v>171000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>144900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>138800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>121800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>95900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>79600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>107200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>122000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>110000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>116700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>111800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>120800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>176300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>229000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,58 +2223,62 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>154900</v>
+      </c>
+      <c r="E41" s="3">
         <v>145800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>147400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>103000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>131300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>131200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>168600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>140900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>102900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>259600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>181600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>291700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>218000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>77300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>73900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2238,58 +2327,64 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E43" s="3">
         <v>60700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>45700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>26700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>49300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>40000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>39900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>75000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>142900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>277600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>69500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>76500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>118000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>19200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>27500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2338,8 +2433,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2388,8 +2486,11 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2438,58 +2539,64 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9962000</v>
+      </c>
+      <c r="E47" s="3">
         <v>9581200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9363400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9703700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9715100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9740000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10156500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10101900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9918000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8274900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7391700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6129300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5607400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4905900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4056700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3650400</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2538,8 +2645,11 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2588,8 +2698,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,58 +2804,64 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E52" s="3">
         <v>14600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>17600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10134600</v>
+      </c>
+      <c r="E54" s="3">
         <v>9802200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9572400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9848000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9909000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9925800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10382700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10331000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10177500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8821700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7652800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6504400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5950900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5011200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4168100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3782500</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,8 +3007,9 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2928,8 +3058,11 @@
       <c r="R57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2978,58 +3111,64 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>270600</v>
+      </c>
+      <c r="E59" s="3">
         <v>237300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>244200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>205600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>222300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>244500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>239400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>259700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>231400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>221600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>151000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>232500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>182700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>135300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>178500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>216900</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3078,58 +3217,64 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4911900</v>
+      </c>
+      <c r="E61" s="3">
         <v>4962400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4978000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5451900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5527700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5512700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5788200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5637400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5498600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4457700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3760700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2946200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2500400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2335000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1708500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1794100</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3178,8 +3323,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5182600</v>
+      </c>
+      <c r="E66" s="3">
         <v>5199600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5222200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5657500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5750000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5757200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6027600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5897100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5730100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4679300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3911700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3178700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2683100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2470300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1886900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2011000</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,58 +3768,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>250000</v>
+      </c>
+      <c r="E72" s="3">
         <v>218600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>181200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>152100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>125700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>99400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>133500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>177100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>202200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>167500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>131600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>81800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>35100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-126900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-308300</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4952000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4602600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4350300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4190500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4159000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4168500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4355100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4433900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4447500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4142500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3741100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3325700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3267800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2540900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2281100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1771500</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>157300</v>
+      </c>
+      <c r="E81" s="3">
         <v>171000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>144900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>138800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>121800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>95900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>79600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>107200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>122000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>110000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>116700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>111800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>120800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>176300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>229000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,8 +4220,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4073,8 +4271,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-127900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-90400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>521300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>155900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>167800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>488000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>36300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-19200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1388600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-924400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1216200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-299300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-660500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-708300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-229600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-721800</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4443,8 +4663,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,8 +4769,11 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4593,8 +4822,11 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,35 +4845,36 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-128100</v>
+      </c>
+      <c r="E96" s="3">
         <v>-111100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-107000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-91800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-117700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-111700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-115800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-78200</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4663,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,96 +5055,102 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>152200</v>
+      </c>
+      <c r="E100" s="3">
         <v>88900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-486500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-186800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-171400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-525400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>57200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1232400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1001700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1105900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>373300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>801200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>711600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>197500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>762400</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>9600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3600</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>8</v>
@@ -4910,57 +5158,63 @@
       <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>44400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-28200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-37500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>27700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>38100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-156700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>78000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-110100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>73700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>140700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-32100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>40500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BXSL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BXSL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>BXSL</t>
   </si>
@@ -656,250 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>304000</v>
+      </c>
+      <c r="E8" s="3">
         <v>304300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>284000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>290400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>264900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>250900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>226800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>187000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>185600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>192000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>166900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>135100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>130700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>136700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>91600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>81200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>80200</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>125900</v>
+        <v>132000</v>
       </c>
       <c r="E9" s="3">
-        <v>112300</v>
+        <v>124400</v>
       </c>
       <c r="F9" s="3">
-        <v>114200</v>
+        <v>113800</v>
       </c>
       <c r="G9" s="3">
-        <v>111500</v>
+        <v>110200</v>
       </c>
       <c r="H9" s="3">
-        <v>106400</v>
+        <v>110000</v>
       </c>
       <c r="I9" s="3">
-        <v>97000</v>
+        <v>103200</v>
       </c>
       <c r="J9" s="3">
+        <v>91600</v>
+      </c>
+      <c r="K9" s="3">
         <v>82600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>78000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>77200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>65300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>54400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>47300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>46300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>33300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>30600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>178400</v>
+        <v>172000</v>
       </c>
       <c r="E10" s="3">
-        <v>171700</v>
+        <v>179900</v>
       </c>
       <c r="F10" s="3">
-        <v>176200</v>
+        <v>170200</v>
       </c>
       <c r="G10" s="3">
-        <v>153400</v>
+        <v>180200</v>
       </c>
       <c r="H10" s="3">
-        <v>144500</v>
+        <v>154900</v>
       </c>
       <c r="I10" s="3">
-        <v>129800</v>
+        <v>147700</v>
       </c>
       <c r="J10" s="3">
+        <v>135200</v>
+      </c>
+      <c r="K10" s="3">
         <v>104400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>107600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>114800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>101600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>80700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>83400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>90400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>58300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>50600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>49200</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -919,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,8 +1042,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1078,8 +1098,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1131,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>134800</v>
+      </c>
+      <c r="E17" s="3">
         <v>127600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>118200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>113900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>113100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>107300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>94600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>81700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>81500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>81000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>70800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>63700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>55100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>51100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>36300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>32700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>169200</v>
+      </c>
+      <c r="E18" s="3">
         <v>176700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>165800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>176500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>151800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>143700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>132200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>105300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>104100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>111000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>96100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>71400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>75600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>85600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>55300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>48500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>50800</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,61 +1309,65 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-15200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>10200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-26700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-21900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-36200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-25700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>11400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>16200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>45300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>35900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>35600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>121000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>180500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-358100</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1382,8 +1419,11 @@
       <c r="S21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1435,79 +1475,85 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>187100</v>
+      </c>
+      <c r="E23" s="3">
         <v>161500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>176000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>149800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>141400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>121800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>95900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>79600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>108600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>122500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>112200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>116700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>111500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>121200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>176300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>229000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-307400</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E24" s="3">
         <v>4200</v>
-      </c>
-      <c r="E24" s="3">
-        <v>5000</v>
       </c>
       <c r="F24" s="3">
         <v>5000</v>
       </c>
       <c r="G24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H24" s="3">
         <v>2600</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
@@ -1515,34 +1561,37 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>1400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2200</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3" t="s">
+      <c r="R24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>183800</v>
+      </c>
+      <c r="E26" s="3">
         <v>157300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>171000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>144900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>138800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>121800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>95900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>79600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>107200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>122000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>110000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>116700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>111800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>120800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>176300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>229000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>183800</v>
+      </c>
+      <c r="E27" s="3">
         <v>157300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>171000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>144900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>138800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>121800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>95900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>79600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>107200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>122000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>110000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>116700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>111800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>120800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>176300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>229000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E32" s="3">
         <v>15200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-10200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>26700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>21900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>36200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>25700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-11400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-16200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-45300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-35900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-35600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-121000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-180500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>358100</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>183800</v>
+      </c>
+      <c r="E33" s="3">
         <v>157300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>171000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>144900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>138800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>121800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>95900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>79600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>107200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>122000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>110000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>116700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>111800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>120800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>176300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>229000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>183800</v>
+      </c>
+      <c r="E35" s="3">
         <v>157300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>171000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>144900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>138800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>121800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>95900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>79600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>107200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>122000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>110000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>116700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>111800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>120800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>176300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>229000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,61 +2310,65 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>147700</v>
+      </c>
+      <c r="E41" s="3">
         <v>154900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>145800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>147400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>103000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>131300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>131200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>168600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>140900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>102900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>259600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>181600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>291700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>218000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>77300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>73900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2330,61 +2420,67 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
         <v>1300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>60700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>45700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>26700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>49300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>40000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>39900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>75000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>142900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>277600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>69500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>76500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>118000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>19200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>27500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2436,8 +2532,11 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2489,8 +2588,11 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2542,61 +2644,67 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>10542600</v>
+      </c>
+      <c r="E47" s="3">
         <v>9962000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9581200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9363400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9703700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9715100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9740000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10156500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10101900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9918000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8274900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7391700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6129300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5607400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4905900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4056700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3650400</v>
       </c>
     </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2648,8 +2756,11 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2701,8 +2812,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,61 +2924,67 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E52" s="3">
         <v>16500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>17600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10705100</v>
+      </c>
+      <c r="E54" s="3">
         <v>10134600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9802200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9572400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9848000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9909000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9925800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10382700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10331000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10177500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8821700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7652800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6504400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5950900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5011200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4168100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3782500</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,8 +3138,9 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3061,8 +3192,11 @@
       <c r="S57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3114,61 +3248,67 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>275300</v>
+      </c>
+      <c r="E59" s="3">
         <v>270600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>237300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>244200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>205600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>222300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>244500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>239400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>259700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>231400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>221600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>151000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>232500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>182700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>135300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>178500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>216900</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3220,61 +3360,67 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5274100</v>
+      </c>
+      <c r="E61" s="3">
         <v>4911900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4962400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4978000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5451900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5527700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5512700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5788200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5637400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5498600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4457700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3760700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2946200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2500400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2335000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1708500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1794100</v>
       </c>
     </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3326,8 +3472,11 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5549400</v>
+      </c>
+      <c r="E66" s="3">
         <v>5182600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5199600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5222200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5657500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5750000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5757200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6027600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5897100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5730100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4679300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3911700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3178700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2683100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2470300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1886900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2011000</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>286000</v>
+      </c>
+      <c r="E72" s="3">
         <v>250000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>218600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>181200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>152100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>125700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>99400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>133500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>177100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>202200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>167500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>131600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>81800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>35100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-126900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-308300</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5155700</v>
+      </c>
+      <c r="E76" s="3">
         <v>4952000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4602600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4350300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4190500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4159000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4168500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4355100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4433900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4447500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4142500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3741100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3325700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3267800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2540900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2281100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1771500</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>183800</v>
+      </c>
+      <c r="E81" s="3">
         <v>157300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>171000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>144900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>138800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>121800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>95900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>79600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>107200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>122000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>110000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>116700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>111800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>120800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>176300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>229000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,8 +4419,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4274,8 +4473,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-395500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-127900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-90400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>521300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>155900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>167800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>488000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>36300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-19200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1388600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-924400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1216200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-299300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-660500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-708300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-229600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-721800</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,8 +4833,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4666,8 +4887,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,8 +4999,11 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4825,8 +5055,11 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,38 +5079,39 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-137400</v>
+      </c>
+      <c r="E96" s="3">
         <v>-128100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-111100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-107000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-91800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-117700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-111700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-115800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-78200</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4899,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,102 +5301,108 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>388300</v>
+      </c>
+      <c r="E100" s="3">
         <v>152200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>88900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-486500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-186800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-171400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-525400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>57200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1232400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1001700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1105900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>373300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>801200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>711600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>197500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>762400</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-15200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>9600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3600</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3" t="s">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-300</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>8</v>
@@ -5161,60 +5410,66 @@
       <c r="R101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E102" s="3">
         <v>9100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>44400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-28200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-37500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>27700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>38100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-156700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>78000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-110100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>73700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>140700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-32100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>40500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BXSL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BXSL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>BXSL</t>
   </si>
@@ -656,263 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>327100</v>
+      </c>
+      <c r="E8" s="3">
         <v>304000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>304300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>284000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>290400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>264900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>250900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>226800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>187000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>185600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>192000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>166900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>135100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>130700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>136700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>91600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>81200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>80200</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>147700</v>
+      </c>
+      <c r="E9" s="3">
         <v>132000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>124400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>113800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>110200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>110000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>103200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>91600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>82600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>78000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>77200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>65300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>54400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>47300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>46300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>33300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>30600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>179400</v>
+      </c>
+      <c r="E10" s="3">
         <v>172000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>179900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>170200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>180200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>154900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>147700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>135200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>104400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>107600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>114800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>101600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>80700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>83400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>90400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>58300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>50600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>49200</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,8 +946,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -989,8 +1003,11 @@
       <c r="T12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,8 +1062,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1101,8 +1121,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>150500</v>
+      </c>
+      <c r="E17" s="3">
         <v>134800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>127600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>118200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>113900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>113100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>107300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>94600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>81700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>81500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>81000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>70800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>63700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>55100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>51100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>36300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>32700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>176600</v>
+      </c>
+      <c r="E18" s="3">
         <v>169200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>176700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>165800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>176500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>151800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>143700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>132200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>105300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>104100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>111000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>96100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>71400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>75600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>85600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>55300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>48500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>50800</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,64 +1343,68 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E20" s="3">
         <v>17900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-15200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>10200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-26700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-10300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-21900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-36200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-25700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>11400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>16200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>45300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>35900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>35600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>121000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>180500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-358100</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1422,8 +1459,11 @@
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1478,64 +1518,70 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>199600</v>
+      </c>
+      <c r="E23" s="3">
         <v>187100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>161500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>176000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>149800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>141400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>121800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>95900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>79600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>108600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>122500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>112200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>116700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>111500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>121200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>176300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>229000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-307400</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1543,20 +1589,20 @@
         <v>3400</v>
       </c>
       <c r="E24" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F24" s="3">
         <v>4200</v>
-      </c>
-      <c r="F24" s="3">
-        <v>5000</v>
       </c>
       <c r="G24" s="3">
         <v>5000</v>
       </c>
       <c r="H24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I24" s="3">
         <v>2600</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -1564,34 +1610,37 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>1400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2200</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3" t="s">
+      <c r="S24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>196200</v>
+      </c>
+      <c r="E26" s="3">
         <v>183800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>157300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>171000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>144900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>138800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>121800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>95900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>79600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>107200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>122000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>110000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>116700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>111800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>120800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>176300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>229000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>196200</v>
+      </c>
+      <c r="E27" s="3">
         <v>183800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>157300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>171000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>144900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>138800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>121800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>95900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>79600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>107200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>122000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>110000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>116700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>111800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>120800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>176300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>229000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-17900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>15200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-10200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>26700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>10300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>21900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>36200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>25700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-11400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-16200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-45300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-35900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-35600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-121000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-180500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>358100</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>196200</v>
+      </c>
+      <c r="E33" s="3">
         <v>183800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>157300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>171000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>144900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>138800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>121800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>95900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>79600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>107200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>122000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>110000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>116700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>111800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>120800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>176300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>229000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>196200</v>
+      </c>
+      <c r="E35" s="3">
         <v>183800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>157300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>171000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>144900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>138800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>121800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>95900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>79600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>107200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>122000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>110000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>116700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>111800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>120800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>176300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>229000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,64 +2397,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>291300</v>
+      </c>
+      <c r="E41" s="3">
         <v>147700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>154900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>145800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>147400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>103000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>131300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>131200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>168600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>140900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>102900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>259600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>181600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>291700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>218000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>77300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>73900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2423,64 +2513,70 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>56400</v>
       </c>
       <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
         <v>1300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>60700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>45700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>26700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>49300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>40000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>39900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>75000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>142900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>277600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>69500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>76500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>118000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>19200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>27500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2535,8 +2631,11 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2591,8 +2690,11 @@
       <c r="T45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2647,64 +2749,70 @@
       <c r="T46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11407700</v>
+      </c>
+      <c r="E47" s="3">
         <v>10542600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9962000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9581200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9363400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9703700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9715100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9740000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10156500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10101900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9918000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8274900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7391700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6129300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5607400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4905900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4056700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3650400</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2759,8 +2867,11 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,64 +3044,70 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E52" s="3">
         <v>14800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>13600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>9400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11770400</v>
+      </c>
+      <c r="E54" s="3">
         <v>10705100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10134600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9802200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9572400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9848000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9909000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9925800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10382700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10331000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10177500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8821700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7652800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6504400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5950900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5011200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4168100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3782500</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,8 +3269,9 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3195,8 +3326,11 @@
       <c r="T57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3251,64 +3385,70 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>291600</v>
+      </c>
+      <c r="E59" s="3">
         <v>275300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>270600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>237300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>244200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>205600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>222300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>244500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>239400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>259700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>231400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>221600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>151000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>232500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>182700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>135300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>178500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>216900</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3363,64 +3503,70 @@
       <c r="T60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6084300</v>
+      </c>
+      <c r="E61" s="3">
         <v>5274100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4911900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4962400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4978000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5451900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5527700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5512700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5788200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5637400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5498600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4457700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3760700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2946200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2500400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2335000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1708500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1794100</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3475,8 +3621,11 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6375800</v>
+      </c>
+      <c r="E66" s="3">
         <v>5549400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5182600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5199600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5222200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5657500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5750000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5757200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6027600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5897100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5730100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4679300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3911700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3178700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2683100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2470300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1886900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2011000</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>329500</v>
+      </c>
+      <c r="E72" s="3">
         <v>286000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>250000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>218600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>181200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>152100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>125700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>99400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>133500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>177100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>202200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>167500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>131600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>81800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>35100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-126900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-308300</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5394600</v>
+      </c>
+      <c r="E76" s="3">
         <v>5155700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4952000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4602600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4350300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4190500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4159000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4168500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4355100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4433900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4447500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4142500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3741100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3325700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3267800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2540900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2281100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1771500</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>196200</v>
+      </c>
+      <c r="E81" s="3">
         <v>183800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>157300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>171000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>144900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>138800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>121800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>95900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>79600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>107200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>122000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>110000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>116700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>111800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>120800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>176300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>229000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4618,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4476,8 +4675,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-709200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-395500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-127900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-90400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>521300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>155900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>167800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>488000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>36300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-19200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1388600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-924400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1216200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-299300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-660500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-708300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-229600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-721800</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,8 +5054,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4890,8 +5111,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,8 +5229,11 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5058,8 +5288,11 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,41 +5313,42 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-142400</v>
+      </c>
+      <c r="E96" s="3">
         <v>-137400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-128100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-111100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-107000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-91800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-117700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-111700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-115800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-78200</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,64 +5547,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>852800</v>
+      </c>
+      <c r="E100" s="3">
         <v>388300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>152200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>88900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-486500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-186800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-171400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-525400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>57200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1232400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1001700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1105900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>373300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>801200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>711600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>197500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>762400</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5369,43 +5618,43 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-15200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>9600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3600</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>8</v>
@@ -5413,63 +5662,69 @@
       <c r="S101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>143600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>44400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-28200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-37500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>27700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>38100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-156700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>78000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-110100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>73700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>140700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-32100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>40500</v>
       </c>
     </row>
